--- a/docs/_baseline/benthos_report.xlsx
+++ b/docs/_baseline/benthos_report.xlsx
@@ -1,14 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <bookViews>
-    <workbookView activeTab="3"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="조사개황" state="visible" r:id="rId1"/>
     <sheet sheetId="2" name="출현종" state="visible" r:id="rId2"/>
     <sheet sheetId="3" name="건강성평가(BMI)" state="visible" r:id="rId3"/>
-    <sheet sheetId="4" name="License" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">출현종!$A$3:$N$7</definedName>
@@ -18,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119">
   <si>
     <t>저서동물 조사결과 — 조사개황</t>
   </si>
@@ -74,16 +70,16 @@
     <t>[ 채집방법 ]</t>
   </si>
   <si>
-    <t>Surber net 30×30</t>
-  </si>
-  <si>
-    <t>Surber net 50×50</t>
-  </si>
-  <si>
-    <t>드렛지</t>
-  </si>
-  <si>
-    <t>에크만</t>
+    <t>Surber 30×30 (회)</t>
+  </si>
+  <si>
+    <t>Surber 50×50 (회)</t>
+  </si>
+  <si>
+    <t>드렛지/D-Net (회)</t>
+  </si>
+  <si>
+    <t>에크만 (회)</t>
   </si>
   <si>
     <t>[ 서식처(하천 이용·식생) ]</t>
@@ -92,7 +88,7 @@
     <t>유역이용</t>
   </si>
   <si>
-    <t>확인가능 오염원</t>
+    <t>확인 가능 오염원</t>
   </si>
   <si>
     <t>식생 수피도</t>
@@ -137,7 +133,7 @@
     <t>[ 서식처(수리·환경) ]</t>
   </si>
   <si>
-    <t>하천형태</t>
+    <t>하천유형(서식처)</t>
   </si>
   <si>
     <t>하폭(m)</t>
@@ -375,9 +371,6 @@
   </si>
   <si>
     <t>E</t>
-  </si>
-  <si>
-    <t>Thank you for using version 2026.2.519.80 of Telerik Document Processing Libraries. License validation couldn't run, possibly due to a missing Telerik.Licensing NuGet package reference to BaselineGen. See documentation for setup. Learn more about Telerik Document Processing Libraries licensing https://docs.telerik.com/devtools/document-processing/distribution-and-licensing/license-key</t>
   </si>
 </sst>
 </file>
@@ -385,7 +378,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <b val="false"/>
       <i val="false"/>
@@ -443,15 +436,6 @@
       <color rgb="FFB71C1C"/>
       <name val="맑은 고딕"/>
     </font>
-    <font>
-      <b val="false"/>
-      <i val="false"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -484,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
     <xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" borderId="0" xfId="0" applyFont="true"/>
@@ -500,7 +484,6 @@
     <xf numFmtId="0" fontId="6" borderId="0" xfId="0" applyFont="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1585,19 +1568,4 @@
   <autoFilter ref="A3:R4"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
-</worksheet>
 </file>
--- a/docs/_baseline/benthos_report.xlsx
+++ b/docs/_baseline/benthos_report.xlsx
@@ -7,14 +7,14 @@
     <sheet sheetId="3" name="건강성평가(BMI)" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">출현종!$A$3:$N$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="true">'건강성평가(BMI)'!$A$3:$R$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">출현종!$A$3:$O$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="true">'건강성평가(BMI)'!$A$3:$T$4</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127">
   <si>
     <t>저서동물 조사결과 — 조사개황</t>
   </si>
@@ -82,6 +82,12 @@
     <t>에크만 (회)</t>
   </si>
   <si>
+    <t>채집 면적(㎡)</t>
+  </si>
+  <si>
+    <t>개체밀도 계산</t>
+  </si>
+  <si>
     <t>[ 서식처(하천 이용·식생) ]</t>
   </si>
   <si>
@@ -205,6 +211,9 @@
     <t>기준픽스처</t>
   </si>
   <si>
+    <t>Surber 30×30 × 3회 = 0.27㎡</t>
+  </si>
+  <si>
     <t>농경지</t>
   </si>
   <si>
@@ -238,6 +247,15 @@
     <t>프로젝트명</t>
   </si>
   <si>
+    <t>※ 개체밀도(inds./㎡) = 실측 개체수 ÷ 채집 면적. 채집 면적 = Σ(채집기 면적 × 조사 횟수) — Surber 30×30 0.09㎡ · Surber 50×50 0.25㎡ · 에크만 0.0225㎡(15×15cm 기준).</t>
+  </si>
+  <si>
+    <t>※ 드렛지/D-Net 은 면적 기준이 없어 환산하지 않는다 — 드렛지/D-Net 이 섞인 조사는 '환산 불가'.</t>
+  </si>
+  <si>
+    <t>※ 지수(BMI·DI·H'·R1·J')는 실측 개체수로 계산한다(개체밀도와 관계없음).</t>
+  </si>
+  <si>
     <t>과업대표하천</t>
   </si>
   <si>
@@ -316,6 +334,9 @@
     <t>개체수</t>
   </si>
   <si>
+    <t>개체밀도(inds./㎡)</t>
+  </si>
+  <si>
     <t>오탁치</t>
   </si>
   <si>
@@ -341,6 +362,9 @@
   </si>
   <si>
     <t>총개체수</t>
+  </si>
+  <si>
+    <t>총 개체밀도(inds./㎡)</t>
   </si>
   <si>
     <t>우점종</t>
@@ -603,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="false" customWidth="true" width="28.57421875" hidden="false" outlineLevel="0"/>
@@ -635,7 +659,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -651,7 +675,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +691,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -675,7 +699,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -683,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -691,7 +715,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -699,7 +723,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -707,7 +731,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -731,7 +755,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -739,7 +763,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -747,7 +771,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -797,41 +821,41 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
+      <c r="A27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="2"/>
+      <c r="A28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>63</v>
-      </c>
+      <c r="A30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="2"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="2" t="n">
-        <v>20</v>
+      <c r="B32" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="33">
@@ -839,15 +863,15 @@
         <v>26</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>66</v>
+      <c r="B34" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -855,45 +879,45 @@
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
+      <c r="A36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37" s="2"/>
+      <c r="A37" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="A39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="2"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -901,7 +925,7 @@
         <v>33</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -925,7 +949,7 @@
         <v>36</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -933,45 +957,45 @@
         <v>37</v>
       </c>
       <c r="B46" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="2" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>68</v>
-      </c>
+      <c r="A50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="2"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>25</v>
-      </c>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B52" s="2" t="n">
-        <v>12</v>
+      <c r="B52" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="53">
@@ -979,7 +1003,7 @@
         <v>42</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54">
@@ -987,7 +1011,7 @@
         <v>43</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>0.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
@@ -995,7 +1019,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>24.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56">
@@ -1003,23 +1027,23 @@
         <v>45</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>19.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>69</v>
+      <c r="B57" s="2" t="n">
+        <v>24.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>70</v>
+      <c r="B58" s="2" t="n">
+        <v>19.2</v>
       </c>
     </row>
     <row r="59">
@@ -1027,40 +1051,56 @@
         <v>48</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
+      <c r="A60" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B61" s="2"/>
+      <c r="A61" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="s">
-        <v>50</v>
+      <c r="A63" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="B63" s="2"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>71</v>
-      </c>
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
     </row>
     <row r="65">
-      <c r="A65" s="2"/>
+      <c r="A65" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="B65" s="2"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
@@ -1069,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="false" customWidth="true" width="12.8515625" hidden="false" outlineLevel="0"/>
@@ -1082,14 +1122,15 @@
     <col min="9" max="9" bestFit="false" customWidth="true" width="21.421875" hidden="false" outlineLevel="0"/>
     <col min="10" max="10" bestFit="false" customWidth="true" width="31.421875" hidden="false" outlineLevel="0"/>
     <col min="11" max="11" bestFit="false" customWidth="true" width="10.7109375" hidden="false" outlineLevel="0"/>
-    <col min="12" max="12" bestFit="false" customWidth="true" width="10.00390625" hidden="false" outlineLevel="0"/>
-    <col min="13" max="13" bestFit="false" customWidth="true" width="12.140625" hidden="false" outlineLevel="0"/>
-    <col min="14" max="14" bestFit="false" customWidth="true" width="10.00390625" hidden="false" outlineLevel="0"/>
+    <col min="12" max="12" bestFit="false" customWidth="true" width="17.140625" hidden="false" outlineLevel="0"/>
+    <col min="13" max="13" bestFit="false" customWidth="true" width="10.00390625" hidden="false" outlineLevel="0"/>
+    <col min="14" max="14" bestFit="false" customWidth="true" width="12.140625" hidden="false" outlineLevel="0"/>
+    <col min="15" max="15" bestFit="false" customWidth="true" width="10.00390625" hidden="false" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1104,6 +1145,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2"/>
@@ -1120,214 +1162,304 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>102</v>
+        <v>108</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="7" t="n">
         <v>250</v>
       </c>
-      <c r="L4" s="2"/>
+      <c r="L4" s="7" t="n">
+        <v>925.9</v>
+      </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>30</v>
       </c>
       <c r="L5" s="7" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="M5" s="7" t="n">
         <v>2.9</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="N5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>5000</v>
       </c>
       <c r="L6" s="7" t="n">
+        <v>18518.5</v>
+      </c>
+      <c r="M6" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="N6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>12</v>
       </c>
       <c r="L7" s="7" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="M7" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="N7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N7"/>
+  <autoFilter ref="A3:O7"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="false" customWidth="true" width="12.8515625" hidden="false" outlineLevel="0"/>
@@ -1338,17 +1470,19 @@
     <col min="7" max="7" bestFit="false" customWidth="true" width="13.57421875" hidden="false" outlineLevel="0"/>
     <col min="8" max="8" bestFit="false" customWidth="true" width="12.8515625" hidden="false" outlineLevel="0"/>
     <col min="9" max="9" bestFit="false" customWidth="true" width="11.421875" hidden="false" outlineLevel="0"/>
-    <col min="10" max="10" bestFit="false" customWidth="true" width="18.57421875" hidden="false" outlineLevel="0"/>
-    <col min="11" max="14" bestFit="false" customWidth="true" width="11.421875" hidden="false" outlineLevel="0"/>
-    <col min="15" max="15" bestFit="false" customWidth="true" width="13.57421875" hidden="false" outlineLevel="0"/>
-    <col min="16" max="16" bestFit="false" customWidth="true" width="12.8515625" hidden="false" outlineLevel="0"/>
-    <col min="17" max="17" bestFit="false" customWidth="true" width="11.421875" hidden="false" outlineLevel="0"/>
-    <col min="18" max="18" bestFit="false" customWidth="true" width="8.57421875" hidden="false" outlineLevel="0"/>
+    <col min="10" max="10" bestFit="false" customWidth="true" width="13.57421875" hidden="false" outlineLevel="0"/>
+    <col min="11" max="11" bestFit="false" customWidth="true" width="21.421875" hidden="false" outlineLevel="0"/>
+    <col min="12" max="12" bestFit="false" customWidth="true" width="18.57421875" hidden="false" outlineLevel="0"/>
+    <col min="13" max="16" bestFit="false" customWidth="true" width="11.421875" hidden="false" outlineLevel="0"/>
+    <col min="17" max="17" bestFit="false" customWidth="true" width="13.57421875" hidden="false" outlineLevel="0"/>
+    <col min="18" max="18" bestFit="false" customWidth="true" width="12.8515625" hidden="false" outlineLevel="0"/>
+    <col min="19" max="19" bestFit="false" customWidth="true" width="11.421875" hidden="false" outlineLevel="0"/>
+    <col min="20" max="20" bestFit="false" customWidth="true" width="8.57421875" hidden="false" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1367,6 +1501,8 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2"/>
@@ -1387,16 +1523,18 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>11</v>
@@ -1408,60 +1546,66 @@
         <v>8</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>46156</v>
@@ -1472,32 +1616,38 @@
       <c r="I4" s="7" t="n">
         <v>5292</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>93</v>
+      <c r="J4" s="7" t="n">
+        <v>0.27</v>
       </c>
       <c r="K4" s="7" t="n">
+        <v>19600</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M4" s="7" t="n">
         <v>0.992</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="N4" s="7" t="n">
         <v>0.348</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="O4" s="7" t="n">
         <v>0.35</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="P4" s="7" t="n">
         <v>0.174</v>
       </c>
-      <c r="O4" s="7" t="n">
+      <c r="Q4" s="7" t="n">
         <v>81.6</v>
       </c>
-      <c r="P4" s="7" t="n">
+      <c r="R4" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="Q4" s="7" t="n">
+      <c r="S4" s="7" t="n">
         <v>27.1</v>
       </c>
-      <c r="R4" s="8" t="s">
-        <v>118</v>
+      <c r="T4" s="8" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="5">
@@ -1519,10 +1669,12 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1541,10 +1693,12 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1563,9 +1717,83 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R4"/>
+  <autoFilter ref="A3:T4"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
 </worksheet>
 </file>
--- a/docs/_baseline/benthos_report.xlsx
+++ b/docs/_baseline/benthos_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125">
   <si>
     <t>저서동물 조사결과 — 조사개황</t>
   </si>
@@ -112,28 +112,22 @@
     <t>[ 서식지 하상구성(%) ]</t>
   </si>
   <si>
-    <t>암반</t>
-  </si>
-  <si>
-    <t>콘크리트</t>
-  </si>
-  <si>
-    <t>진흙이하(&lt;0.063mm)</t>
-  </si>
-  <si>
-    <t>모래(0.063-2mm)</t>
-  </si>
-  <si>
-    <t>잔자갈(2-16mm)</t>
-  </si>
-  <si>
-    <t>자갈(16-64mm)</t>
-  </si>
-  <si>
-    <t>작은돌(64-256mm)</t>
-  </si>
-  <si>
-    <t>큰돌(&gt;256mm)</t>
+    <t>진흙 이하(&lt;0.063mm)</t>
+  </si>
+  <si>
+    <t>모래(0.063~2mm)</t>
+  </si>
+  <si>
+    <t>왕모래(2~16mm)</t>
+  </si>
+  <si>
+    <t>자갈(16~64mm)</t>
+  </si>
+  <si>
+    <t>작은돌(64~256mm)</t>
+  </si>
+  <si>
+    <t>큰돌 이상(&gt;256mm)</t>
   </si>
   <si>
     <t>[ 서식처(수리·환경) ]</t>
@@ -627,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="false" customWidth="true" width="28.57421875" hidden="false" outlineLevel="0"/>
@@ -659,7 +653,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +669,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -691,7 +685,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -699,7 +693,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -707,7 +701,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -715,7 +709,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -723,7 +717,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
@@ -731,7 +725,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -755,7 +749,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -763,7 +757,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +765,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -833,7 +827,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
@@ -855,7 +849,7 @@
         <v>25</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33">
@@ -863,7 +857,7 @@
         <v>26</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34">
@@ -879,7 +873,7 @@
         <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36">
@@ -887,7 +881,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37">
@@ -895,7 +889,7 @@
         <v>30</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38">
@@ -917,7 +911,7 @@
         <v>32</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -925,7 +919,7 @@
         <v>33</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -949,7 +943,7 @@
         <v>36</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -957,45 +951,45 @@
         <v>37</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="2" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="B48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B50" s="2"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
+      <c r="B51" s="2" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>71</v>
+      <c r="B52" s="2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="53">
@@ -1003,7 +997,7 @@
         <v>42</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
@@ -1011,7 +1005,7 @@
         <v>43</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>12</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="55">
@@ -1019,7 +1013,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>35</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="56">
@@ -1027,23 +1021,23 @@
         <v>45</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>0.4</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="2" t="n">
-        <v>24.5</v>
+      <c r="B57" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B58" s="2" t="n">
-        <v>19.2</v>
+      <c r="B58" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="59">
@@ -1051,56 +1045,40 @@
         <v>48</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="B61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B63" s="2"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
+      <c r="B64" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A65" s="2"/>
       <c r="B65" s="2"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
@@ -1130,7 +1108,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1166,70 +1144,70 @@
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K3" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="7" t="n">
@@ -1244,34 +1222,34 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>30</v>
@@ -1289,34 +1267,34 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>5000</v>
@@ -1334,34 +1312,34 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>12</v>
@@ -1396,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1415,7 +1393,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1434,7 +1412,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1482,7 +1460,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1528,13 +1506,13 @@
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>11</v>
@@ -1546,66 +1524,66 @@
         <v>8</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="S3" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="T3" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>46156</v>
@@ -1623,7 +1601,7 @@
         <v>19600</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>0.992</v>
@@ -1647,7 +1625,7 @@
         <v>27.1</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5">
@@ -1674,7 +1652,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1698,7 +1676,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1722,7 +1700,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1746,7 +1724,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1770,7 +1748,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
